--- a/public/exports-60-250/26696348.xlsx
+++ b/public/exports-60-250/26696348.xlsx
@@ -8239,7 +8239,7 @@
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t xml:space="preserve">200033703</t>
+          <t xml:space="preserve">200033702</t>
         </is>
       </c>
       <c r="L110" t="inlineStr">
@@ -11239,7 +11239,7 @@
       </c>
       <c r="K150" t="inlineStr">
         <is>
-          <t xml:space="preserve">311878990</t>
+          <t xml:space="preserve">311878986</t>
         </is>
       </c>
       <c r="L150" t="inlineStr">
@@ -11314,7 +11314,7 @@
       </c>
       <c r="K151" t="inlineStr">
         <is>
-          <t xml:space="preserve">311878990</t>
+          <t xml:space="preserve">311878986</t>
         </is>
       </c>
       <c r="L151" t="inlineStr">
@@ -11389,7 +11389,7 @@
       </c>
       <c r="K152" t="inlineStr">
         <is>
-          <t xml:space="preserve">311878990</t>
+          <t xml:space="preserve">311878986</t>
         </is>
       </c>
       <c r="L152" t="inlineStr">
@@ -11464,7 +11464,7 @@
       </c>
       <c r="K153" t="inlineStr">
         <is>
-          <t xml:space="preserve">311878990</t>
+          <t xml:space="preserve">311878986</t>
         </is>
       </c>
       <c r="L153" t="inlineStr">
@@ -11539,7 +11539,7 @@
       </c>
       <c r="K154" t="inlineStr">
         <is>
-          <t xml:space="preserve">311878990</t>
+          <t xml:space="preserve">311878986</t>
         </is>
       </c>
       <c r="L154" t="inlineStr">
@@ -11614,7 +11614,7 @@
       </c>
       <c r="K155" t="inlineStr">
         <is>
-          <t xml:space="preserve">311878990</t>
+          <t xml:space="preserve">311878986</t>
         </is>
       </c>
       <c r="L155" t="inlineStr">
